--- a/examples/Mythras_Character_Sheet_Enhanced.xlsx
+++ b/examples/Mythras_Character_Sheet_Enhanced.xlsx
@@ -658,7 +658,7 @@
         </is>
       </c>
       <c r="E9">
-        <f>SUM(B:B)</f>
+        <f>SUM(I:I)</f>
         <v/>
       </c>
       <c r="N9" s="3" t="inlineStr">
@@ -677,7 +677,7 @@
         </is>
       </c>
       <c r="E10">
-        <f>SUM(C:C)</f>
+        <f>SUM(J:J)</f>
         <v/>
       </c>
       <c r="N10" s="3" t="inlineStr">
